--- a/output/nabos_03_02avg.xlsx
+++ b/output/nabos_03_02avg.xlsx
@@ -544,76 +544,76 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3.959</v>
+        <v>3.948</v>
       </c>
       <c r="B2" t="n">
         <v>74.46048</v>
       </c>
       <c r="C2" t="n">
-        <v>169.90819</v>
+        <v>169.9082</v>
       </c>
       <c r="D2" t="n">
         <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.3149</v>
+        <v>-1.3157</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.2985</v>
+        <v>-1.2998</v>
       </c>
       <c r="G2" t="n">
-        <v>22.264263</v>
+        <v>22.258418</v>
       </c>
       <c r="H2" t="n">
-        <v>22.340761</v>
+        <v>22.336312</v>
       </c>
       <c r="I2" t="n">
-        <v>27.3054</v>
+        <v>27.2991</v>
       </c>
       <c r="J2" t="n">
-        <v>27.3929</v>
+        <v>27.3887</v>
       </c>
       <c r="K2" t="n">
-        <v>371.031</v>
+        <v>371.233</v>
       </c>
       <c r="L2" t="n">
-        <v>361.38</v>
+        <v>361.382</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2363</v>
+        <v>0.253</v>
       </c>
       <c r="N2" t="n">
-        <v>4.5963</v>
+        <v>4.5969</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1068</v>
+        <v>0.1063</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1068</v>
+        <v>0.1063</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0798</v>
+        <v>0.0793</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0345</v>
+        <v>0.0351</v>
       </c>
       <c r="S2" t="n">
-        <v>1458</v>
+        <v>1475</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0116</v>
+        <v>1.0233</v>
       </c>
       <c r="U2" t="n">
-        <v>54.98</v>
+        <v>54.97</v>
       </c>
       <c r="V2" t="n">
-        <v>2.57</v>
+        <v>2.571</v>
       </c>
       <c r="W2" t="n">
-        <v>2.2307</v>
+        <v>2.2306</v>
       </c>
       <c r="X2" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -636,7 +636,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4.948</v>
+        <v>4.95</v>
       </c>
       <c r="B3" t="n">
         <v>74.46048</v>
@@ -651,61 +651,61 @@
         <v>-1.3159</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.315</v>
+        <v>-1.3167</v>
       </c>
       <c r="G3" t="n">
-        <v>22.26934</v>
+        <v>22.269954</v>
       </c>
       <c r="H3" t="n">
-        <v>22.271658</v>
+        <v>22.262957</v>
       </c>
       <c r="I3" t="n">
-        <v>27.3126</v>
+        <v>27.3136</v>
       </c>
       <c r="J3" t="n">
-        <v>27.3149</v>
+        <v>27.3052</v>
       </c>
       <c r="K3" t="n">
-        <v>371.149</v>
+        <v>371.106</v>
       </c>
       <c r="L3" t="n">
-        <v>361.682</v>
+        <v>361.7</v>
       </c>
       <c r="M3" t="n">
         <v>0.1966</v>
       </c>
       <c r="N3" t="n">
-        <v>4.5933</v>
+        <v>4.5928</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1054</v>
+        <v>0.1057</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1054</v>
+        <v>0.1057</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0825</v>
+        <v>0.083</v>
       </c>
       <c r="R3" t="n">
         <v>0.0329</v>
       </c>
       <c r="S3" t="n">
-        <v>1788</v>
+        <v>1794</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2411</v>
+        <v>1.245</v>
       </c>
       <c r="U3" t="n">
-        <v>54.18</v>
+        <v>54.16</v>
       </c>
       <c r="V3" t="n">
-        <v>2.5705</v>
+        <v>2.5702</v>
       </c>
       <c r="W3" t="n">
-        <v>2.23</v>
+        <v>2.2298</v>
       </c>
       <c r="X3" t="n">
-        <v>19</v>
+        <v>94</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -740,43 +740,43 @@
         <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.3151</v>
+        <v>-1.3152</v>
       </c>
       <c r="F4" t="n">
         <v>-1.3147</v>
       </c>
       <c r="G4" t="n">
-        <v>22.272876</v>
+        <v>22.271669</v>
       </c>
       <c r="H4" t="n">
-        <v>22.272432</v>
+        <v>22.271833</v>
       </c>
       <c r="I4" t="n">
-        <v>27.3161</v>
+        <v>27.3146</v>
       </c>
       <c r="J4" t="n">
-        <v>27.3151</v>
+        <v>27.3144</v>
       </c>
       <c r="K4" t="n">
-        <v>371.433</v>
+        <v>371.343</v>
       </c>
       <c r="L4" t="n">
-        <v>360.722</v>
+        <v>361.142</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1887</v>
+        <v>0.189</v>
       </c>
       <c r="N4" t="n">
-        <v>4.5934</v>
+        <v>4.5931</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1061</v>
+        <v>0.1063</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1061</v>
+        <v>0.1063</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0824</v>
+        <v>0.0827</v>
       </c>
       <c r="R4" t="n">
         <v>0.0326</v>
@@ -788,16 +788,16 @@
         <v>1.3664</v>
       </c>
       <c r="U4" t="n">
-        <v>53.13</v>
+        <v>53.06</v>
       </c>
       <c r="V4" t="n">
-        <v>2.5719</v>
+        <v>2.5714</v>
       </c>
       <c r="W4" t="n">
-        <v>2.2252</v>
+        <v>2.2272</v>
       </c>
       <c r="X4" t="n">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -835,37 +835,37 @@
         <v>-1.3101</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.3125</v>
+        <v>-1.3128</v>
       </c>
       <c r="G5" t="n">
-        <v>22.309936</v>
+        <v>22.309423</v>
       </c>
       <c r="H5" t="n">
-        <v>22.284333</v>
+        <v>22.280639</v>
       </c>
       <c r="I5" t="n">
-        <v>27.3607</v>
+        <v>27.3599</v>
       </c>
       <c r="J5" t="n">
-        <v>27.3285</v>
+        <v>27.3239</v>
       </c>
       <c r="K5" t="n">
-        <v>371.04</v>
+        <v>371.027</v>
       </c>
       <c r="L5" t="n">
-        <v>360.983</v>
+        <v>360.981</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1673</v>
+        <v>0.1666</v>
       </c>
       <c r="N5" t="n">
         <v>4.5933</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1059</v>
+        <v>0.1057</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1059</v>
+        <v>0.1057</v>
       </c>
       <c r="Q5" t="n">
         <v>0.0825</v>
@@ -874,22 +874,22 @@
         <v>0.0316</v>
       </c>
       <c r="S5" t="n">
-        <v>2055</v>
+        <v>2058</v>
       </c>
       <c r="T5" t="n">
-        <v>1.4267</v>
+        <v>1.4283</v>
       </c>
       <c r="U5" t="n">
-        <v>52.1</v>
+        <v>52.07</v>
       </c>
       <c r="V5" t="n">
         <v>2.5704</v>
       </c>
       <c r="W5" t="n">
-        <v>2.2265</v>
+        <v>2.2264</v>
       </c>
       <c r="X5" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -912,7 +912,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7.917</v>
+        <v>7.916</v>
       </c>
       <c r="B6" t="n">
         <v>74.46048</v>
@@ -924,64 +924,64 @@
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3111</v>
+        <v>-1.3115</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3109</v>
+        <v>-1.311</v>
       </c>
       <c r="G6" t="n">
-        <v>22.29971</v>
+        <v>22.294772</v>
       </c>
       <c r="H6" t="n">
-        <v>22.295451</v>
+        <v>22.292802</v>
       </c>
       <c r="I6" t="n">
-        <v>27.3473</v>
+        <v>27.341</v>
       </c>
       <c r="J6" t="n">
-        <v>27.3415</v>
+        <v>27.3379</v>
       </c>
       <c r="K6" t="n">
-        <v>371.442</v>
+        <v>371.465</v>
       </c>
       <c r="L6" t="n">
-        <v>361.579</v>
+        <v>361.667</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1962</v>
+        <v>0.1927</v>
       </c>
       <c r="N6" t="n">
         <v>4.5941</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1017</v>
+        <v>0.1019</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1017</v>
+        <v>0.1019</v>
       </c>
       <c r="Q6" t="n">
         <v>0.0818</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0329</v>
+        <v>0.0327</v>
       </c>
       <c r="S6" t="n">
-        <v>2126</v>
+        <v>2127</v>
       </c>
       <c r="T6" t="n">
-        <v>1.476</v>
+        <v>1.4763</v>
       </c>
       <c r="U6" t="n">
-        <v>34.7</v>
+        <v>35.24</v>
       </c>
       <c r="V6" t="n">
         <v>2.5722</v>
       </c>
       <c r="W6" t="n">
-        <v>2.2294</v>
+        <v>2.2297</v>
       </c>
       <c r="X6" t="n">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1004,7 +1004,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>8.907</v>
+        <v>8.908</v>
       </c>
       <c r="B7" t="n">
         <v>74.46048</v>
@@ -1016,64 +1016,64 @@
         <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2809</v>
+        <v>-1.2811</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2878</v>
+        <v>-1.2875</v>
       </c>
       <c r="G7" t="n">
-        <v>22.460014</v>
+        <v>22.459624</v>
       </c>
       <c r="H7" t="n">
-        <v>22.419316</v>
+        <v>22.423395</v>
       </c>
       <c r="I7" t="n">
-        <v>27.534</v>
+        <v>27.5326</v>
       </c>
       <c r="J7" t="n">
-        <v>27.4858</v>
+        <v>27.4901</v>
       </c>
       <c r="K7" t="n">
-        <v>370.574</v>
+        <v>370.6</v>
       </c>
       <c r="L7" t="n">
-        <v>360.951</v>
+        <v>360.89</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1819</v>
+        <v>0.179</v>
       </c>
       <c r="N7" t="n">
-        <v>4.5941</v>
+        <v>4.5943</v>
       </c>
       <c r="O7" t="n">
-        <v>0.101</v>
+        <v>0.1007</v>
       </c>
       <c r="P7" t="n">
-        <v>0.101</v>
+        <v>0.1007</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0817</v>
+        <v>0.0816</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0323</v>
+        <v>0.0321</v>
       </c>
       <c r="S7" t="n">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="T7" t="n">
-        <v>1.5137</v>
+        <v>1.515</v>
       </c>
       <c r="U7" t="n">
-        <v>18.04</v>
+        <v>17.45</v>
       </c>
       <c r="V7" t="n">
-        <v>2.572</v>
+        <v>2.5721</v>
       </c>
       <c r="W7" t="n">
-        <v>2.2293</v>
+        <v>2.2291</v>
       </c>
       <c r="X7" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -1096,7 +1096,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>9.896</v>
+        <v>9.897</v>
       </c>
       <c r="B8" t="n">
         <v>74.46048</v>
@@ -1108,64 +1108,64 @@
         <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2665</v>
+        <v>-1.2661</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2683</v>
+        <v>-1.2682</v>
       </c>
       <c r="G8" t="n">
-        <v>22.535022</v>
+        <v>22.537841</v>
       </c>
       <c r="H8" t="n">
-        <v>22.520686</v>
+        <v>22.521191</v>
       </c>
       <c r="I8" t="n">
-        <v>27.6208</v>
+        <v>27.623</v>
       </c>
       <c r="J8" t="n">
-        <v>27.6032</v>
+        <v>27.6026</v>
       </c>
       <c r="K8" t="n">
-        <v>370.19</v>
+        <v>370.142</v>
       </c>
       <c r="L8" t="n">
-        <v>360.427</v>
+        <v>360.507</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1971</v>
+        <v>0.198</v>
       </c>
       <c r="N8" t="n">
         <v>4.5934</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1034</v>
+        <v>0.1033</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1034</v>
+        <v>0.1033</v>
       </c>
       <c r="Q8" t="n">
         <v>0.0824</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0329</v>
+        <v>0.033</v>
       </c>
       <c r="S8" t="n">
-        <v>2232</v>
+        <v>2234</v>
       </c>
       <c r="T8" t="n">
-        <v>1.5492</v>
+        <v>1.551</v>
       </c>
       <c r="U8" t="n">
-        <v>34.82</v>
+        <v>36.86</v>
       </c>
       <c r="V8" t="n">
-        <v>2.5719</v>
+        <v>2.5717</v>
       </c>
       <c r="W8" t="n">
-        <v>2.2292</v>
+        <v>2.2296</v>
       </c>
       <c r="X8" t="n">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -1200,55 +1200,55 @@
         <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2777</v>
+        <v>-1.2801</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2769</v>
+        <v>-1.2772</v>
       </c>
       <c r="G9" t="n">
-        <v>22.469805</v>
+        <v>22.456374</v>
       </c>
       <c r="H9" t="n">
-        <v>22.474485</v>
+        <v>22.472659</v>
       </c>
       <c r="I9" t="n">
-        <v>27.5431</v>
+        <v>27.527</v>
       </c>
       <c r="J9" t="n">
-        <v>27.5487</v>
+        <v>27.5461</v>
       </c>
       <c r="K9" t="n">
-        <v>370.72</v>
+        <v>370.788</v>
       </c>
       <c r="L9" t="n">
-        <v>360.534</v>
+        <v>360.542</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1977</v>
+        <v>0.199</v>
       </c>
       <c r="N9" t="n">
-        <v>4.5916</v>
+        <v>4.5917</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1028</v>
+        <v>0.1034</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1028</v>
+        <v>0.1034</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0839</v>
+        <v>0.0838</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0329</v>
+        <v>0.033</v>
       </c>
       <c r="S9" t="n">
-        <v>2296</v>
+        <v>2297</v>
       </c>
       <c r="T9" t="n">
-        <v>1.5938</v>
+        <v>1.5942</v>
       </c>
       <c r="U9" t="n">
-        <v>33.75</v>
+        <v>35.48</v>
       </c>
       <c r="V9" t="n">
         <v>2.5726</v>
@@ -1257,7 +1257,7 @@
         <v>2.2283</v>
       </c>
       <c r="X9" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1292,64 +1292,64 @@
         <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.301</v>
+        <v>-1.3025</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2939</v>
+        <v>-1.2947</v>
       </c>
       <c r="G10" t="n">
-        <v>22.336105</v>
+        <v>22.327181</v>
       </c>
       <c r="H10" t="n">
-        <v>22.375319</v>
+        <v>22.370675</v>
       </c>
       <c r="I10" t="n">
-        <v>27.3848</v>
+        <v>27.3745</v>
       </c>
       <c r="J10" t="n">
-        <v>27.4308</v>
+        <v>27.4255</v>
       </c>
       <c r="K10" t="n">
-        <v>371.487</v>
+        <v>371.455</v>
       </c>
       <c r="L10" t="n">
-        <v>361.326</v>
+        <v>361.464</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1847</v>
+        <v>0.1827</v>
       </c>
       <c r="N10" t="n">
-        <v>4.5924</v>
+        <v>4.5925</v>
       </c>
       <c r="O10" t="n">
-        <v>0.104</v>
+        <v>0.1039</v>
       </c>
       <c r="P10" t="n">
-        <v>0.104</v>
+        <v>0.1039</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0833</v>
+        <v>0.0832</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0324</v>
+        <v>0.0323</v>
       </c>
       <c r="S10" t="n">
-        <v>2350</v>
+        <v>2351</v>
       </c>
       <c r="T10" t="n">
-        <v>1.6312</v>
+        <v>1.6322</v>
       </c>
       <c r="U10" t="n">
-        <v>38.21</v>
+        <v>38.11</v>
       </c>
       <c r="V10" t="n">
-        <v>2.5726</v>
+        <v>2.5721</v>
       </c>
       <c r="W10" t="n">
-        <v>2.2294</v>
+        <v>2.2299</v>
       </c>
       <c r="X10" t="n">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1372,7 +1372,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>12.865</v>
+        <v>12.864</v>
       </c>
       <c r="B11" t="n">
         <v>74.46048</v>
@@ -1384,34 +1384,34 @@
         <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2569</v>
+        <v>-1.2564</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2509</v>
+        <v>-1.2492</v>
       </c>
       <c r="G11" t="n">
-        <v>22.597663</v>
+        <v>22.600999</v>
       </c>
       <c r="H11" t="n">
-        <v>22.618882</v>
+        <v>22.631108</v>
       </c>
       <c r="I11" t="n">
-        <v>27.6942</v>
+        <v>27.6971</v>
       </c>
       <c r="J11" t="n">
-        <v>27.7171</v>
+        <v>27.7306</v>
       </c>
       <c r="K11" t="n">
-        <v>369.987</v>
+        <v>369.977</v>
       </c>
       <c r="L11" t="n">
-        <v>360.294</v>
+        <v>360.185</v>
       </c>
       <c r="M11" t="n">
-        <v>0.19</v>
+        <v>0.1872</v>
       </c>
       <c r="N11" t="n">
-        <v>4.5914</v>
+        <v>4.5915</v>
       </c>
       <c r="O11" t="n">
         <v>0.1019</v>
@@ -1420,28 +1420,28 @@
         <v>0.1019</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0842</v>
+        <v>0.0841</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0326</v>
+        <v>0.0324</v>
       </c>
       <c r="S11" t="n">
-        <v>2403</v>
+        <v>2404</v>
       </c>
       <c r="T11" t="n">
-        <v>1.6682</v>
+        <v>1.669</v>
       </c>
       <c r="U11" t="n">
-        <v>30.56</v>
+        <v>31.09</v>
       </c>
       <c r="V11" t="n">
-        <v>2.5717</v>
+        <v>2.5718</v>
       </c>
       <c r="W11" t="n">
-        <v>2.2303</v>
+        <v>2.2301</v>
       </c>
       <c r="X11" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -1464,7 +1464,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>13.854</v>
+        <v>13.856</v>
       </c>
       <c r="B12" t="n">
         <v>74.46048</v>
@@ -1476,34 +1476,34 @@
         <v>14</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.2519</v>
+        <v>-1.2523</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2541</v>
+        <v>-1.2533</v>
       </c>
       <c r="G12" t="n">
-        <v>22.625441</v>
+        <v>22.624139</v>
       </c>
       <c r="H12" t="n">
-        <v>22.607491</v>
+        <v>22.61234</v>
       </c>
       <c r="I12" t="n">
-        <v>27.7263</v>
+        <v>27.724</v>
       </c>
       <c r="J12" t="n">
-        <v>27.7043</v>
+        <v>27.7092</v>
       </c>
       <c r="K12" t="n">
-        <v>370.073</v>
+        <v>370.105</v>
       </c>
       <c r="L12" t="n">
-        <v>360.307</v>
+        <v>360.283</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2277</v>
+        <v>0.2229</v>
       </c>
       <c r="N12" t="n">
-        <v>4.5923</v>
+        <v>4.5924</v>
       </c>
       <c r="O12" t="n">
         <v>0.103</v>
@@ -1512,28 +1512,28 @@
         <v>0.103</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0834</v>
+        <v>0.0833</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0341</v>
+        <v>0.0339</v>
       </c>
       <c r="S12" t="n">
-        <v>2453</v>
+        <v>2455</v>
       </c>
       <c r="T12" t="n">
-        <v>1.7029</v>
+        <v>1.7041</v>
       </c>
       <c r="U12" t="n">
-        <v>8.49</v>
+        <v>6.48</v>
       </c>
       <c r="V12" t="n">
-        <v>2.5728</v>
+        <v>2.573</v>
       </c>
       <c r="W12" t="n">
         <v>2.2299</v>
       </c>
       <c r="X12" t="n">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -1556,7 +1556,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>14.844</v>
+        <v>14.842</v>
       </c>
       <c r="B13" t="n">
         <v>74.46048</v>
@@ -1568,64 +1568,64 @@
         <v>15</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.2556</v>
+        <v>-1.2567</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.2615</v>
+        <v>-1.2627</v>
       </c>
       <c r="G13" t="n">
-        <v>22.609423</v>
+        <v>22.604877</v>
       </c>
       <c r="H13" t="n">
-        <v>22.575056</v>
+        <v>22.569256</v>
       </c>
       <c r="I13" t="n">
-        <v>27.7078</v>
+        <v>27.7022</v>
       </c>
       <c r="J13" t="n">
-        <v>27.6672</v>
+        <v>27.6602</v>
       </c>
       <c r="K13" t="n">
-        <v>370.267</v>
+        <v>370.274</v>
       </c>
       <c r="L13" t="n">
-        <v>360.66</v>
+        <v>360.792</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2011</v>
+        <v>0.204</v>
       </c>
       <c r="N13" t="n">
-        <v>4.5927</v>
+        <v>4.5926</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1045</v>
+        <v>0.1043</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1045</v>
+        <v>0.1043</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.083</v>
+        <v>0.0832</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0331</v>
+        <v>0.0332</v>
       </c>
       <c r="S13" t="n">
-        <v>2514</v>
+        <v>2515</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7454</v>
+        <v>1.746</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.46</v>
+        <v>-0.22</v>
       </c>
       <c r="V13" t="n">
-        <v>2.5731</v>
+        <v>2.573</v>
       </c>
       <c r="W13" t="n">
-        <v>2.2304</v>
+        <v>2.2309</v>
       </c>
       <c r="X13" t="n">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -1648,7 +1648,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>15.834</v>
+        <v>15.836</v>
       </c>
       <c r="B14" t="n">
         <v>74.46048</v>
@@ -1660,64 +1660,64 @@
         <v>16</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.2728</v>
+        <v>-1.2685</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.2749</v>
+        <v>-1.2731</v>
       </c>
       <c r="G14" t="n">
-        <v>22.54307</v>
+        <v>22.572929</v>
       </c>
       <c r="H14" t="n">
-        <v>22.519392</v>
+        <v>22.531038</v>
       </c>
       <c r="I14" t="n">
-        <v>27.6342</v>
+        <v>27.6702</v>
       </c>
       <c r="J14" t="n">
-        <v>27.6044</v>
+        <v>27.6185</v>
       </c>
       <c r="K14" t="n">
-        <v>370.823</v>
+        <v>370.688</v>
       </c>
       <c r="L14" t="n">
-        <v>361.013</v>
+        <v>360.908</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2275</v>
+        <v>0.2202</v>
       </c>
       <c r="N14" t="n">
-        <v>4.5923</v>
+        <v>4.5926</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1036</v>
+        <v>0.1037</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1036</v>
+        <v>0.1037</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.0834</v>
+        <v>0.0831</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0341</v>
+        <v>0.0338</v>
       </c>
       <c r="S14" t="n">
-        <v>2559</v>
+        <v>2561</v>
       </c>
       <c r="T14" t="n">
-        <v>1.7763</v>
+        <v>1.7778</v>
       </c>
       <c r="U14" t="n">
-        <v>0.09</v>
+        <v>0.07</v>
       </c>
       <c r="V14" t="n">
-        <v>2.5736</v>
+        <v>2.5738</v>
       </c>
       <c r="W14" t="n">
-        <v>2.2303</v>
+        <v>2.2301</v>
       </c>
       <c r="X14" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -1740,7 +1740,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>16.823</v>
+        <v>16.821</v>
       </c>
       <c r="B15" t="n">
         <v>74.46048</v>
@@ -1752,64 +1752,64 @@
         <v>17</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.2485</v>
+        <v>-1.2477</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.2488</v>
+        <v>-1.2466</v>
       </c>
       <c r="G15" t="n">
-        <v>22.725482</v>
+        <v>22.732555</v>
       </c>
       <c r="H15" t="n">
-        <v>22.720095</v>
+        <v>22.737752</v>
       </c>
       <c r="I15" t="n">
-        <v>27.8557</v>
+        <v>27.8639</v>
       </c>
       <c r="J15" t="n">
-        <v>27.8488</v>
+        <v>27.8697</v>
       </c>
       <c r="K15" t="n">
-        <v>370.163</v>
+        <v>370.101</v>
       </c>
       <c r="L15" t="n">
-        <v>360.043</v>
+        <v>360.015</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2339</v>
+        <v>0.2349</v>
       </c>
       <c r="N15" t="n">
-        <v>4.5934</v>
+        <v>4.5932</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1038</v>
+        <v>0.1041</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1038</v>
+        <v>0.1041</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.0824</v>
+        <v>0.0826</v>
       </c>
       <c r="R15" t="n">
         <v>0.0344</v>
       </c>
       <c r="S15" t="n">
-        <v>2627</v>
+        <v>2630</v>
       </c>
       <c r="T15" t="n">
-        <v>1.824</v>
+        <v>1.8254</v>
       </c>
       <c r="U15" t="n">
-        <v>37.5</v>
+        <v>39.92</v>
       </c>
       <c r="V15" t="n">
-        <v>2.5748</v>
+        <v>2.5747</v>
       </c>
       <c r="W15" t="n">
-        <v>2.2302</v>
+        <v>2.2304</v>
       </c>
       <c r="X15" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
@@ -1832,10 +1832,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>17.813</v>
+        <v>17.812</v>
       </c>
       <c r="B16" t="n">
-        <v>74.46048</v>
+        <v>74.46047</v>
       </c>
       <c r="C16" t="n">
         <v>169.90864</v>
@@ -1844,64 +1844,64 @@
         <v>18</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.2489</v>
+        <v>-1.2475</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2491</v>
+        <v>-1.2469</v>
       </c>
       <c r="G16" t="n">
-        <v>22.721496</v>
+        <v>22.732339</v>
       </c>
       <c r="H16" t="n">
-        <v>22.716848</v>
+        <v>22.729969</v>
       </c>
       <c r="I16" t="n">
-        <v>27.8502</v>
+        <v>27.863</v>
       </c>
       <c r="J16" t="n">
-        <v>27.8442</v>
+        <v>27.8592</v>
       </c>
       <c r="K16" t="n">
-        <v>370.189</v>
+        <v>370.12</v>
       </c>
       <c r="L16" t="n">
-        <v>360.475</v>
+        <v>360.495</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2615</v>
+        <v>0.2587</v>
       </c>
       <c r="N16" t="n">
-        <v>4.5908</v>
+        <v>4.5909</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1045</v>
+        <v>0.1046</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1045</v>
+        <v>0.1046</v>
       </c>
       <c r="Q16" t="n">
         <v>0.0846</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0355</v>
+        <v>0.0353</v>
       </c>
       <c r="S16" t="n">
-        <v>2679</v>
+        <v>2680</v>
       </c>
       <c r="T16" t="n">
-        <v>1.86</v>
+        <v>1.8603</v>
       </c>
       <c r="U16" t="n">
-        <v>40.88</v>
+        <v>40.25</v>
       </c>
       <c r="V16" t="n">
-        <v>2.5746</v>
+        <v>2.5745</v>
       </c>
       <c r="W16" t="n">
-        <v>2.2319</v>
+        <v>2.2323</v>
       </c>
       <c r="X16" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -1924,7 +1924,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>18.802</v>
+        <v>18.805</v>
       </c>
       <c r="B17" t="n">
         <v>74.46046</v>
@@ -1936,64 +1936,64 @@
         <v>19</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1124</v>
+        <v>-1.1226</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1418</v>
+        <v>-1.1381</v>
       </c>
       <c r="G17" t="n">
-        <v>23.475642</v>
+        <v>23.439092</v>
       </c>
       <c r="H17" t="n">
-        <v>23.327939</v>
+        <v>23.353699</v>
       </c>
       <c r="I17" t="n">
-        <v>28.7319</v>
+        <v>28.6883</v>
       </c>
       <c r="J17" t="n">
-        <v>28.5619</v>
+        <v>28.589</v>
       </c>
       <c r="K17" t="n">
-        <v>366.465</v>
+        <v>366.857</v>
       </c>
       <c r="L17" t="n">
-        <v>357.737</v>
+        <v>357.484</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3136</v>
+        <v>0.3339</v>
       </c>
       <c r="N17" t="n">
-        <v>4.5926</v>
+        <v>4.5923</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1052</v>
+        <v>0.1053</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1052</v>
+        <v>0.1053</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.0831</v>
+        <v>0.0834</v>
       </c>
       <c r="R17" t="n">
-        <v>0.0376</v>
+        <v>0.0384</v>
       </c>
       <c r="S17" t="n">
-        <v>2718</v>
+        <v>2720</v>
       </c>
       <c r="T17" t="n">
-        <v>1.8865</v>
+        <v>1.888</v>
       </c>
       <c r="U17" t="n">
-        <v>2</v>
+        <v>5.7</v>
       </c>
       <c r="V17" t="n">
-        <v>2.5764</v>
+        <v>2.5772</v>
       </c>
       <c r="W17" t="n">
-        <v>2.2339</v>
+        <v>2.2332</v>
       </c>
       <c r="X17" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
@@ -2016,7 +2016,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>19.792</v>
+        <v>19.791</v>
       </c>
       <c r="B18" t="n">
         <v>74.46046</v>
@@ -2028,64 +2028,64 @@
         <v>20</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.133</v>
+        <v>-1.1335</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1325</v>
+        <v>-1.1331</v>
       </c>
       <c r="G18" t="n">
-        <v>23.541899</v>
+        <v>23.543974</v>
       </c>
       <c r="H18" t="n">
-        <v>23.524499</v>
+        <v>23.526385</v>
       </c>
       <c r="I18" t="n">
-        <v>28.84</v>
+        <v>28.8408</v>
       </c>
       <c r="J18" t="n">
-        <v>28.8162</v>
+        <v>28.8166</v>
       </c>
       <c r="K18" t="n">
-        <v>367.13</v>
+        <v>367.123</v>
       </c>
       <c r="L18" t="n">
-        <v>357.054</v>
+        <v>357.146</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4019</v>
+        <v>0.4035</v>
       </c>
       <c r="N18" t="n">
-        <v>4.5879</v>
+        <v>4.5873</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1078</v>
+        <v>0.1079</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1078</v>
+        <v>0.1079</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.0872</v>
+        <v>0.0877</v>
       </c>
       <c r="R18" t="n">
         <v>0.0411</v>
       </c>
       <c r="S18" t="n">
-        <v>2783</v>
+        <v>2785</v>
       </c>
       <c r="T18" t="n">
-        <v>1.9317</v>
+        <v>1.9332</v>
       </c>
       <c r="U18" t="n">
-        <v>29.43</v>
+        <v>31.02</v>
       </c>
       <c r="V18" t="n">
-        <v>2.5804</v>
+        <v>2.5803</v>
       </c>
       <c r="W18" t="n">
-        <v>2.2343</v>
+        <v>2.2347</v>
       </c>
       <c r="X18" t="n">
-        <v>26</v>
+        <v>77</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
@@ -2108,7 +2108,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>20.781</v>
+        <v>20.779</v>
       </c>
       <c r="B19" t="n">
         <v>74.46046</v>
@@ -2120,64 +2120,64 @@
         <v>21</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1462</v>
+        <v>-1.1474</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1457</v>
+        <v>-1.1468</v>
       </c>
       <c r="G19" t="n">
-        <v>23.570764</v>
+        <v>23.571713</v>
       </c>
       <c r="H19" t="n">
-        <v>23.569764</v>
+        <v>23.570677</v>
       </c>
       <c r="I19" t="n">
-        <v>28.891</v>
+        <v>28.8921</v>
       </c>
       <c r="J19" t="n">
-        <v>28.8891</v>
+        <v>28.89</v>
       </c>
       <c r="K19" t="n">
-        <v>367.295</v>
+        <v>367.345</v>
       </c>
       <c r="L19" t="n">
-        <v>356.5</v>
+        <v>356.464</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4134</v>
+        <v>0.4147</v>
       </c>
       <c r="N19" t="n">
-        <v>4.5824</v>
+        <v>4.5825</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1084</v>
+        <v>0.1086</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1084</v>
+        <v>0.1086</v>
       </c>
       <c r="Q19" t="n">
         <v>0.0919</v>
       </c>
       <c r="R19" t="n">
-        <v>0.0415</v>
+        <v>0.0416</v>
       </c>
       <c r="S19" t="n">
-        <v>2846</v>
+        <v>2847</v>
       </c>
       <c r="T19" t="n">
-        <v>1.9757</v>
+        <v>1.9761</v>
       </c>
       <c r="U19" t="n">
-        <v>9.66</v>
+        <v>8.97</v>
       </c>
       <c r="V19" t="n">
-        <v>2.581</v>
+        <v>2.5812</v>
       </c>
       <c r="W19" t="n">
-        <v>2.2317</v>
+        <v>2.2315</v>
       </c>
       <c r="X19" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -2200,7 +2200,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>21.771</v>
+        <v>21.772</v>
       </c>
       <c r="B20" t="n">
         <v>74.46046</v>
@@ -2212,34 +2212,34 @@
         <v>22</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1801</v>
+        <v>-1.1809</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1799</v>
+        <v>-1.1808</v>
       </c>
       <c r="G20" t="n">
-        <v>23.59184</v>
+        <v>23.592817</v>
       </c>
       <c r="H20" t="n">
-        <v>23.590315</v>
+        <v>23.591232</v>
       </c>
       <c r="I20" t="n">
-        <v>28.9515</v>
+        <v>28.9536</v>
       </c>
       <c r="J20" t="n">
-        <v>28.9493</v>
+        <v>28.9513</v>
       </c>
       <c r="K20" t="n">
-        <v>367.962</v>
+        <v>367.976</v>
       </c>
       <c r="L20" t="n">
-        <v>356.702</v>
+        <v>356.949</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4699</v>
+        <v>0.4665</v>
       </c>
       <c r="N20" t="n">
-        <v>4.5817</v>
+        <v>4.5819</v>
       </c>
       <c r="O20" t="n">
         <v>0.1087</v>
@@ -2248,28 +2248,28 @@
         <v>0.1087</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.0927</v>
+        <v>0.0925</v>
       </c>
       <c r="R20" t="n">
-        <v>0.0438</v>
+        <v>0.0437</v>
       </c>
       <c r="S20" t="n">
-        <v>2885</v>
+        <v>2886</v>
       </c>
       <c r="T20" t="n">
-        <v>2.0028</v>
+        <v>2.0035</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.04</v>
+        <v>0.21</v>
       </c>
       <c r="V20" t="n">
         <v>2.5834</v>
       </c>
       <c r="W20" t="n">
-        <v>2.2315</v>
+        <v>2.2326</v>
       </c>
       <c r="X20" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
@@ -2292,7 +2292,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>22.76</v>
+        <v>22.762</v>
       </c>
       <c r="B21" t="n">
         <v>74.46046</v>
@@ -2304,55 +2304,55 @@
         <v>23</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2006</v>
+        <v>-1.199</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2012</v>
+        <v>-1.1996</v>
       </c>
       <c r="G21" t="n">
-        <v>23.629788</v>
+        <v>23.632799</v>
       </c>
       <c r="H21" t="n">
-        <v>23.625765</v>
+        <v>23.628332</v>
       </c>
       <c r="I21" t="n">
-        <v>29.0218</v>
+        <v>29.0248</v>
       </c>
       <c r="J21" t="n">
-        <v>29.017</v>
+        <v>29.0194</v>
       </c>
       <c r="K21" t="n">
-        <v>368.933</v>
+        <v>368.913</v>
       </c>
       <c r="L21" t="n">
-        <v>357.789</v>
+        <v>357.778</v>
       </c>
       <c r="M21" t="n">
-        <v>0.474</v>
+        <v>0.4718</v>
       </c>
       <c r="N21" t="n">
-        <v>4.5848</v>
+        <v>4.5846</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1102</v>
+        <v>0.1105</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1102</v>
+        <v>0.1105</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.09</v>
+        <v>0.0901</v>
       </c>
       <c r="R21" t="n">
-        <v>0.044</v>
+        <v>0.0439</v>
       </c>
       <c r="S21" t="n">
-        <v>2934</v>
+        <v>2937</v>
       </c>
       <c r="T21" t="n">
-        <v>2.0366</v>
+        <v>2.039</v>
       </c>
       <c r="U21" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="V21" t="n">
         <v>2.5885</v>
@@ -2361,7 +2361,7 @@
         <v>2.2363</v>
       </c>
       <c r="X21" t="n">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -2384,7 +2384,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>23.75</v>
+        <v>23.749</v>
       </c>
       <c r="B22" t="n">
         <v>74.46046</v>
@@ -2396,34 +2396,34 @@
         <v>24</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1897</v>
+        <v>-1.1901</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.19</v>
+        <v>-1.1903</v>
       </c>
       <c r="G22" t="n">
-        <v>23.697345</v>
+        <v>23.698822</v>
       </c>
       <c r="H22" t="n">
-        <v>23.694351</v>
+        <v>23.695931</v>
       </c>
       <c r="I22" t="n">
-        <v>29.1016</v>
+        <v>29.104</v>
       </c>
       <c r="J22" t="n">
-        <v>29.0978</v>
+        <v>29.1004</v>
       </c>
       <c r="K22" t="n">
-        <v>369.385</v>
+        <v>369.417</v>
       </c>
       <c r="L22" t="n">
-        <v>358.678</v>
+        <v>358.689</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3933</v>
+        <v>0.3928</v>
       </c>
       <c r="N22" t="n">
-        <v>4.5891</v>
+        <v>4.5894</v>
       </c>
       <c r="O22" t="n">
         <v>0.1105</v>
@@ -2432,28 +2432,28 @@
         <v>0.1105</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.0861</v>
+        <v>0.0859</v>
       </c>
       <c r="R22" t="n">
         <v>0.0407</v>
       </c>
       <c r="S22" t="n">
-        <v>3000</v>
+        <v>3002</v>
       </c>
       <c r="T22" t="n">
-        <v>2.0827</v>
+        <v>2.0839</v>
       </c>
       <c r="U22" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="V22" t="n">
-        <v>2.5928</v>
+        <v>2.593</v>
       </c>
       <c r="W22" t="n">
-        <v>2.242</v>
+        <v>2.2421</v>
       </c>
       <c r="X22" t="n">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
@@ -2488,64 +2488,64 @@
         <v>25</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.2484</v>
+        <v>-1.2503</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2476</v>
+        <v>-1.2494</v>
       </c>
       <c r="G23" t="n">
-        <v>23.71273</v>
+        <v>23.711408</v>
       </c>
       <c r="H23" t="n">
-        <v>23.711535</v>
+        <v>23.710238</v>
       </c>
       <c r="I23" t="n">
-        <v>29.179</v>
+        <v>29.181</v>
       </c>
       <c r="J23" t="n">
-        <v>29.1765</v>
+        <v>29.1785</v>
       </c>
       <c r="K23" t="n">
-        <v>371.944</v>
+        <v>372.034</v>
       </c>
       <c r="L23" t="n">
-        <v>360.426</v>
+        <v>360.483</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3969</v>
+        <v>0.3971</v>
       </c>
       <c r="N23" t="n">
-        <v>4.5965</v>
+        <v>4.5967</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1104</v>
+        <v>0.1106</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1104</v>
+        <v>0.1106</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.0797</v>
+        <v>0.0795</v>
       </c>
       <c r="R23" t="n">
         <v>0.0409</v>
       </c>
       <c r="S23" t="n">
-        <v>3057</v>
+        <v>3059</v>
       </c>
       <c r="T23" t="n">
-        <v>2.1223</v>
+        <v>2.1234</v>
       </c>
       <c r="U23" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="V23" t="n">
-        <v>2.6045</v>
+        <v>2.605</v>
       </c>
       <c r="W23" t="n">
-        <v>2.2482</v>
+        <v>2.2484</v>
       </c>
       <c r="X23" t="n">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>25.729</v>
+        <v>25.727</v>
       </c>
       <c r="B24" t="n">
         <v>74.46046</v>
@@ -2580,52 +2580,52 @@
         <v>26</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.2578</v>
+        <v>-1.2579</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.2573</v>
+        <v>-1.2575</v>
       </c>
       <c r="G24" t="n">
-        <v>23.757648</v>
+        <v>23.757494</v>
       </c>
       <c r="H24" t="n">
-        <v>23.756416</v>
+        <v>23.756202</v>
       </c>
       <c r="I24" t="n">
-        <v>29.2481</v>
+        <v>29.2496</v>
       </c>
       <c r="J24" t="n">
-        <v>29.246</v>
+        <v>29.2474</v>
       </c>
       <c r="K24" t="n">
-        <v>372.351</v>
+        <v>372.345</v>
       </c>
       <c r="L24" t="n">
-        <v>361.934</v>
+        <v>361.924</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3689</v>
+        <v>0.3719</v>
       </c>
       <c r="N24" t="n">
-        <v>4.602</v>
+        <v>4.6019</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1113</v>
+        <v>0.1112</v>
       </c>
       <c r="P24" t="n">
-        <v>0.1113</v>
+        <v>0.1112</v>
       </c>
       <c r="Q24" t="n">
         <v>0.075</v>
       </c>
       <c r="R24" t="n">
-        <v>0.0398</v>
+        <v>0.0399</v>
       </c>
       <c r="S24" t="n">
-        <v>3109</v>
+        <v>3110</v>
       </c>
       <c r="T24" t="n">
-        <v>2.1584</v>
+        <v>2.1591</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2637,7 +2637,7 @@
         <v>2.2556</v>
       </c>
       <c r="X24" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="Y24" t="n">
         <v>0</v>
@@ -2660,7 +2660,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>26.718</v>
+        <v>26.721</v>
       </c>
       <c r="B25" t="n">
         <v>74.46046</v>
@@ -2672,64 +2672,64 @@
         <v>27</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.2635</v>
+        <v>-1.2655</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.2637</v>
+        <v>-1.2655</v>
       </c>
       <c r="G25" t="n">
-        <v>23.792767</v>
+        <v>23.78976</v>
       </c>
       <c r="H25" t="n">
-        <v>23.791482</v>
+        <v>23.788494</v>
       </c>
       <c r="I25" t="n">
-        <v>29.3006</v>
+        <v>29.3</v>
       </c>
       <c r="J25" t="n">
-        <v>29.2991</v>
+        <v>29.2983</v>
       </c>
       <c r="K25" t="n">
-        <v>371.422</v>
+        <v>371.41</v>
       </c>
       <c r="L25" t="n">
-        <v>360.971</v>
+        <v>360.97</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3265</v>
+        <v>0.3282</v>
       </c>
       <c r="N25" t="n">
-        <v>4.6052</v>
+        <v>4.6055</v>
       </c>
       <c r="O25" t="n">
-        <v>0.11</v>
+        <v>0.1102</v>
       </c>
       <c r="P25" t="n">
-        <v>0.11</v>
+        <v>0.1102</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.0722</v>
+        <v>0.0719</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0381</v>
+        <v>0.0382</v>
       </c>
       <c r="S25" t="n">
-        <v>3150</v>
+        <v>3152</v>
       </c>
       <c r="T25" t="n">
-        <v>2.1869</v>
+        <v>2.1882</v>
       </c>
       <c r="U25" t="n">
-        <v>0.02</v>
+        <v>0.07</v>
       </c>
       <c r="V25" t="n">
-        <v>2.6021</v>
+        <v>2.6019</v>
       </c>
       <c r="W25" t="n">
-        <v>2.2512</v>
+        <v>2.2511</v>
       </c>
       <c r="X25" t="n">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
@@ -2752,7 +2752,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>27.708</v>
+        <v>27.707</v>
       </c>
       <c r="B26" t="n">
         <v>74.46046</v>
@@ -2764,64 +2764,64 @@
         <v>28</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.2905</v>
+        <v>-1.2914</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.2889</v>
+        <v>-1.2895</v>
       </c>
       <c r="G26" t="n">
-        <v>23.790798</v>
+        <v>23.789459</v>
       </c>
       <c r="H26" t="n">
-        <v>23.789639</v>
+        <v>23.788308</v>
       </c>
       <c r="I26" t="n">
-        <v>29.3239</v>
+        <v>29.3247</v>
       </c>
       <c r="J26" t="n">
-        <v>29.3207</v>
+        <v>29.3212</v>
       </c>
       <c r="K26" t="n">
-        <v>369.749</v>
+        <v>369.73</v>
       </c>
       <c r="L26" t="n">
-        <v>359.624</v>
+        <v>359.635</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2963</v>
+        <v>0.2969</v>
       </c>
       <c r="N26" t="n">
-        <v>4.6114</v>
+        <v>4.6116</v>
       </c>
       <c r="O26" t="n">
-        <v>0.1104</v>
+        <v>0.1103</v>
       </c>
       <c r="P26" t="n">
-        <v>0.1104</v>
+        <v>0.1103</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.0667</v>
+        <v>0.0666</v>
       </c>
       <c r="R26" t="n">
-        <v>0.0368</v>
+        <v>0.0369</v>
       </c>
       <c r="S26" t="n">
-        <v>3215</v>
+        <v>3217</v>
       </c>
       <c r="T26" t="n">
-        <v>2.2316</v>
+        <v>2.2333</v>
       </c>
       <c r="U26" t="n">
-        <v>9.7</v>
+        <v>11.47</v>
       </c>
       <c r="V26" t="n">
-        <v>2.5909</v>
+        <v>2.5908</v>
       </c>
       <c r="W26" t="n">
         <v>2.2435</v>
       </c>
       <c r="X26" t="n">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -2844,7 +2844,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>28.698</v>
+        <v>28.697</v>
       </c>
       <c r="B27" t="n">
         <v>74.46046</v>
@@ -2856,64 +2856,64 @@
         <v>29</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.3294</v>
+        <v>-1.3302</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.3298</v>
+        <v>-1.3306</v>
       </c>
       <c r="G27" t="n">
-        <v>23.779294</v>
+        <v>23.777243</v>
       </c>
       <c r="H27" t="n">
-        <v>23.777803</v>
+        <v>23.775723</v>
       </c>
       <c r="I27" t="n">
-        <v>29.346</v>
+        <v>29.3465</v>
       </c>
       <c r="J27" t="n">
-        <v>29.3444</v>
+        <v>29.3449</v>
       </c>
       <c r="K27" t="n">
-        <v>367.391</v>
+        <v>367.367</v>
       </c>
       <c r="L27" t="n">
-        <v>357.664</v>
+        <v>357.648</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2568</v>
+        <v>0.2567</v>
       </c>
       <c r="N27" t="n">
-        <v>4.6199</v>
+        <v>4.6201</v>
       </c>
       <c r="O27" t="n">
-        <v>0.1102</v>
+        <v>0.1099</v>
       </c>
       <c r="P27" t="n">
-        <v>0.1102</v>
+        <v>0.1099</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.0594</v>
+        <v>0.0592</v>
       </c>
       <c r="R27" t="n">
         <v>0.0353</v>
       </c>
       <c r="S27" t="n">
-        <v>3274</v>
+        <v>3275</v>
       </c>
       <c r="T27" t="n">
-        <v>2.2727</v>
+        <v>2.2736</v>
       </c>
       <c r="U27" t="n">
-        <v>13.73</v>
+        <v>14.67</v>
       </c>
       <c r="V27" t="n">
-        <v>2.5752</v>
+        <v>2.575</v>
       </c>
       <c r="W27" t="n">
-        <v>2.232</v>
+        <v>2.2319</v>
       </c>
       <c r="X27" t="n">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>29.687</v>
+        <v>29.688</v>
       </c>
       <c r="B28" t="n">
         <v>74.46046</v>
@@ -2948,64 +2948,64 @@
         <v>30</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.3553</v>
+        <v>-1.3557</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.3553</v>
+        <v>-1.3558</v>
       </c>
       <c r="G28" t="n">
-        <v>23.776655</v>
+        <v>23.774694</v>
       </c>
       <c r="H28" t="n">
-        <v>23.775312</v>
+        <v>23.77336</v>
       </c>
       <c r="I28" t="n">
-        <v>29.3673</v>
+        <v>29.3677</v>
       </c>
       <c r="J28" t="n">
-        <v>29.3656</v>
+        <v>29.366</v>
       </c>
       <c r="K28" t="n">
-        <v>366.057</v>
+        <v>366.035</v>
       </c>
       <c r="L28" t="n">
-        <v>355.722</v>
+        <v>355.787</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1666</v>
+        <v>0.166</v>
       </c>
       <c r="N28" t="n">
         <v>4.6248</v>
       </c>
       <c r="O28" t="n">
-        <v>0.1112</v>
+        <v>0.1113</v>
       </c>
       <c r="P28" t="n">
-        <v>0.1112</v>
+        <v>0.1113</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.0552</v>
+        <v>0.0551</v>
       </c>
       <c r="R28" t="n">
-        <v>0.0317</v>
+        <v>0.0316</v>
       </c>
       <c r="S28" t="n">
-        <v>3320</v>
+        <v>3321</v>
       </c>
       <c r="T28" t="n">
-        <v>2.3051</v>
+        <v>2.3057</v>
       </c>
       <c r="U28" t="n">
-        <v>0.15</v>
+        <v>0.08</v>
       </c>
       <c r="V28" t="n">
-        <v>2.566</v>
+        <v>2.5659</v>
       </c>
       <c r="W28" t="n">
-        <v>2.2214</v>
+        <v>2.2217</v>
       </c>
       <c r="X28" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="Y28" t="n">
         <v>0</v>
@@ -3040,34 +3040,34 @@
         <v>31</v>
       </c>
       <c r="E29" t="n">
+        <v>-1.3705</v>
+      </c>
+      <c r="F29" t="n">
         <v>-1.3701</v>
       </c>
-      <c r="F29" t="n">
-        <v>-1.3697</v>
-      </c>
       <c r="G29" t="n">
-        <v>23.779</v>
+        <v>23.777328</v>
       </c>
       <c r="H29" t="n">
-        <v>23.777628</v>
+        <v>23.775983</v>
       </c>
       <c r="I29" t="n">
-        <v>29.3845</v>
+        <v>29.385</v>
       </c>
       <c r="J29" t="n">
-        <v>29.3823</v>
+        <v>29.3828</v>
       </c>
       <c r="K29" t="n">
-        <v>365.422</v>
+        <v>365.415</v>
       </c>
       <c r="L29" t="n">
-        <v>355.444</v>
+        <v>355.465</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1651</v>
+        <v>0.1641</v>
       </c>
       <c r="N29" t="n">
-        <v>4.6256</v>
+        <v>4.6257</v>
       </c>
       <c r="O29" t="n">
         <v>0.111</v>
@@ -3076,16 +3076,16 @@
         <v>0.111</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.0545</v>
+        <v>0.0543</v>
       </c>
       <c r="R29" t="n">
-        <v>0.0316</v>
+        <v>0.0315</v>
       </c>
       <c r="S29" t="n">
-        <v>3371</v>
+        <v>3373</v>
       </c>
       <c r="T29" t="n">
-        <v>2.3406</v>
+        <v>2.3416</v>
       </c>
       <c r="U29" t="n">
         <v>0.01</v>
@@ -3094,10 +3094,10 @@
         <v>2.5615</v>
       </c>
       <c r="W29" t="n">
-        <v>2.2193</v>
+        <v>2.2194</v>
       </c>
       <c r="X29" t="n">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -3120,7 +3120,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>31.666</v>
+        <v>31.665</v>
       </c>
       <c r="B30" t="n">
         <v>74.46046</v>
@@ -3132,64 +3132,64 @@
         <v>32</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.3868</v>
+        <v>-1.3873</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.3862</v>
+        <v>-1.3867</v>
       </c>
       <c r="G30" t="n">
-        <v>23.785758</v>
+        <v>23.784368</v>
       </c>
       <c r="H30" t="n">
-        <v>23.784383</v>
+        <v>23.783007</v>
       </c>
       <c r="I30" t="n">
-        <v>29.4096</v>
+        <v>29.4104</v>
       </c>
       <c r="J30" t="n">
-        <v>29.4071</v>
+        <v>29.4079</v>
       </c>
       <c r="K30" t="n">
-        <v>365.483</v>
+        <v>365.478</v>
       </c>
       <c r="L30" t="n">
-        <v>354.87</v>
+        <v>354.815</v>
       </c>
       <c r="M30" t="n">
-        <v>0.1653</v>
+        <v>0.1635</v>
       </c>
       <c r="N30" t="n">
-        <v>4.6252</v>
+        <v>4.6255</v>
       </c>
       <c r="O30" t="n">
-        <v>0.1119</v>
+        <v>0.112</v>
       </c>
       <c r="P30" t="n">
-        <v>0.1119</v>
+        <v>0.112</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.0548</v>
+        <v>0.0546</v>
       </c>
       <c r="R30" t="n">
-        <v>0.0316</v>
+        <v>0.0315</v>
       </c>
       <c r="S30" t="n">
-        <v>3432</v>
+        <v>3434</v>
       </c>
       <c r="T30" t="n">
-        <v>2.3827</v>
+        <v>2.384</v>
       </c>
       <c r="U30" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="V30" t="n">
-        <v>2.561</v>
+        <v>2.5609</v>
       </c>
       <c r="W30" t="n">
-        <v>2.2158</v>
+        <v>2.2156</v>
       </c>
       <c r="X30" t="n">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
@@ -3224,34 +3224,34 @@
         <v>33</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.4006</v>
+        <v>-1.401</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.4004</v>
+        <v>-1.4008</v>
       </c>
       <c r="G31" t="n">
-        <v>23.800064</v>
+        <v>23.799094</v>
       </c>
       <c r="H31" t="n">
-        <v>23.798698</v>
+        <v>23.797763</v>
       </c>
       <c r="I31" t="n">
-        <v>29.4421</v>
+        <v>29.4431</v>
       </c>
       <c r="J31" t="n">
-        <v>29.44</v>
+        <v>29.441</v>
       </c>
       <c r="K31" t="n">
-        <v>364.749</v>
+        <v>364.746</v>
       </c>
       <c r="L31" t="n">
-        <v>352.734</v>
+        <v>352.616</v>
       </c>
       <c r="M31" t="n">
-        <v>0.124</v>
+        <v>0.1238</v>
       </c>
       <c r="N31" t="n">
-        <v>4.629</v>
+        <v>4.6294</v>
       </c>
       <c r="O31" t="n">
         <v>0.1117</v>
@@ -3260,28 +3260,28 @@
         <v>0.1117</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.0515</v>
+        <v>0.0512</v>
       </c>
       <c r="R31" t="n">
         <v>0.0299</v>
       </c>
       <c r="S31" t="n">
-        <v>3488</v>
+        <v>3490</v>
       </c>
       <c r="T31" t="n">
-        <v>2.4215</v>
+        <v>2.4228</v>
       </c>
       <c r="U31" t="n">
         <v>0.06</v>
       </c>
       <c r="V31" t="n">
-        <v>2.5562</v>
+        <v>2.5561</v>
       </c>
       <c r="W31" t="n">
-        <v>2.2051</v>
+        <v>2.2045</v>
       </c>
       <c r="X31" t="n">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="Y31" t="n">
         <v>0</v>
@@ -3304,7 +3304,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>33.645</v>
+        <v>33.644</v>
       </c>
       <c r="B32" t="n">
         <v>74.46046</v>
@@ -3316,34 +3316,34 @@
         <v>34</v>
       </c>
       <c r="E32" t="n">
+        <v>-1.4128</v>
+      </c>
+      <c r="F32" t="n">
         <v>-1.4125</v>
       </c>
-      <c r="F32" t="n">
-        <v>-1.4122</v>
-      </c>
       <c r="G32" t="n">
-        <v>23.816604</v>
+        <v>23.815638</v>
       </c>
       <c r="H32" t="n">
-        <v>23.815362</v>
+        <v>23.814392</v>
       </c>
       <c r="I32" t="n">
-        <v>29.4757</v>
+        <v>29.4765</v>
       </c>
       <c r="J32" t="n">
-        <v>29.4737</v>
+        <v>29.4745</v>
       </c>
       <c r="K32" t="n">
-        <v>363.353</v>
+        <v>363.319</v>
       </c>
       <c r="L32" t="n">
-        <v>319.772</v>
+        <v>317.073</v>
       </c>
       <c r="M32" t="n">
-        <v>0.1399</v>
+        <v>0.1404</v>
       </c>
       <c r="N32" t="n">
-        <v>4.6306</v>
+        <v>4.6305</v>
       </c>
       <c r="O32" t="n">
         <v>0.1116</v>
@@ -3358,22 +3358,22 @@
         <v>0.0306</v>
       </c>
       <c r="S32" t="n">
-        <v>3539</v>
+        <v>3540</v>
       </c>
       <c r="T32" t="n">
-        <v>2.457</v>
+        <v>2.4579</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>2.5478</v>
+        <v>2.5476</v>
       </c>
       <c r="W32" t="n">
-        <v>2.0472</v>
+        <v>2.0343</v>
       </c>
       <c r="X32" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="Y32" t="n">
         <v>0</v>
@@ -3396,7 +3396,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>34.634</v>
+        <v>34.636</v>
       </c>
       <c r="B33" t="n">
         <v>74.46046</v>
@@ -3408,34 +3408,34 @@
         <v>35</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.4158</v>
+        <v>-1.4159</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.4155</v>
+        <v>-1.4157</v>
       </c>
       <c r="G33" t="n">
-        <v>23.847284</v>
+        <v>23.846802</v>
       </c>
       <c r="H33" t="n">
-        <v>23.84616</v>
+        <v>23.845662</v>
       </c>
       <c r="I33" t="n">
-        <v>29.52</v>
+        <v>29.521</v>
       </c>
       <c r="J33" t="n">
-        <v>29.5181</v>
+        <v>29.5191</v>
       </c>
       <c r="K33" t="n">
-        <v>361.066</v>
+        <v>360.976</v>
       </c>
       <c r="L33" t="n">
-        <v>280.391</v>
+        <v>273.382</v>
       </c>
       <c r="M33" t="n">
-        <v>0.1821</v>
+        <v>0.1899</v>
       </c>
       <c r="N33" t="n">
-        <v>4.6289</v>
+        <v>4.6288</v>
       </c>
       <c r="O33" t="n">
         <v>0.1123</v>
@@ -3444,28 +3444,28 @@
         <v>0.1123</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.0516</v>
+        <v>0.0517</v>
       </c>
       <c r="R33" t="n">
-        <v>0.0323</v>
+        <v>0.0326</v>
       </c>
       <c r="S33" t="n">
-        <v>3584</v>
+        <v>3586</v>
       </c>
       <c r="T33" t="n">
-        <v>2.4882</v>
+        <v>2.4894</v>
       </c>
       <c r="U33" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="V33" t="n">
-        <v>2.5351</v>
+        <v>2.5346</v>
       </c>
       <c r="W33" t="n">
-        <v>1.8591</v>
+        <v>1.8256</v>
       </c>
       <c r="X33" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -3488,7 +3488,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>35.624</v>
+        <v>35.623</v>
       </c>
       <c r="B34" t="n">
         <v>74.46046</v>
@@ -3500,64 +3500,64 @@
         <v>36</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.4299</v>
+        <v>-1.4307</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.4291</v>
+        <v>-1.4298</v>
       </c>
       <c r="G34" t="n">
-        <v>23.876773</v>
+        <v>23.876926</v>
       </c>
       <c r="H34" t="n">
-        <v>23.874427</v>
+        <v>23.874358</v>
       </c>
       <c r="I34" t="n">
-        <v>29.5734</v>
+        <v>29.5758</v>
       </c>
       <c r="J34" t="n">
-        <v>29.5695</v>
+        <v>29.5715</v>
       </c>
       <c r="K34" t="n">
-        <v>357.566</v>
+        <v>357.313</v>
       </c>
       <c r="L34" t="n">
-        <v>251.017</v>
+        <v>256.483</v>
       </c>
       <c r="M34" t="n">
-        <v>0.2291</v>
+        <v>0.2278</v>
       </c>
       <c r="N34" t="n">
-        <v>4.6276</v>
+        <v>4.6282</v>
       </c>
       <c r="O34" t="n">
-        <v>0.1132</v>
+        <v>0.1133</v>
       </c>
       <c r="P34" t="n">
-        <v>0.1132</v>
+        <v>0.1133</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.0528</v>
+        <v>0.0522</v>
       </c>
       <c r="R34" t="n">
-        <v>0.0342</v>
+        <v>0.0341</v>
       </c>
       <c r="S34" t="n">
-        <v>3647</v>
+        <v>3650</v>
       </c>
       <c r="T34" t="n">
-        <v>2.5317</v>
+        <v>2.5337</v>
       </c>
       <c r="U34" t="n">
         <v>0.08</v>
       </c>
       <c r="V34" t="n">
-        <v>2.515</v>
+        <v>2.5136</v>
       </c>
       <c r="W34" t="n">
-        <v>1.7185</v>
+        <v>1.7446</v>
       </c>
       <c r="X34" t="n">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="Y34" t="n">
         <v>0</v>
@@ -3592,31 +3592,31 @@
         <v>37</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.4439</v>
+        <v>-1.4444</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.444</v>
+        <v>-1.4445</v>
       </c>
       <c r="G35" t="n">
-        <v>23.923223</v>
+        <v>23.923477</v>
       </c>
       <c r="H35" t="n">
-        <v>23.922426</v>
+        <v>23.922722</v>
       </c>
       <c r="I35" t="n">
-        <v>29.6499</v>
+        <v>29.6521</v>
       </c>
       <c r="J35" t="n">
-        <v>29.6488</v>
+        <v>29.6512</v>
       </c>
       <c r="K35" t="n">
-        <v>354.713</v>
+        <v>354.555</v>
       </c>
       <c r="L35" t="n">
-        <v>242.306</v>
+        <v>242.125</v>
       </c>
       <c r="M35" t="n">
-        <v>0.2297</v>
+        <v>0.2284</v>
       </c>
       <c r="N35" t="n">
         <v>4.6248</v>
@@ -3631,25 +3631,25 @@
         <v>0.0552</v>
       </c>
       <c r="R35" t="n">
-        <v>0.0342</v>
+        <v>0.0341</v>
       </c>
       <c r="S35" t="n">
-        <v>3705</v>
+        <v>3707</v>
       </c>
       <c r="T35" t="n">
-        <v>2.5722</v>
+        <v>2.5733</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>2.499</v>
+        <v>2.4981</v>
       </c>
       <c r="W35" t="n">
-        <v>1.6769</v>
+        <v>1.676</v>
       </c>
       <c r="X35" t="n">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
@@ -3672,7 +3672,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>37.603</v>
+        <v>37.604</v>
       </c>
       <c r="B36" t="n">
         <v>74.46046</v>
@@ -3684,64 +3684,64 @@
         <v>38</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.46</v>
+        <v>-1.4617</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.4601</v>
+        <v>-1.4618</v>
       </c>
       <c r="G36" t="n">
-        <v>23.985215</v>
+        <v>23.984531</v>
       </c>
       <c r="H36" t="n">
-        <v>23.983921</v>
+        <v>23.983222</v>
       </c>
       <c r="I36" t="n">
-        <v>29.7496</v>
+        <v>29.752</v>
       </c>
       <c r="J36" t="n">
-        <v>29.7479</v>
+        <v>29.7504</v>
       </c>
       <c r="K36" t="n">
-        <v>349.116</v>
+        <v>348.856</v>
       </c>
       <c r="L36" t="n">
-        <v>232.895</v>
+        <v>232.479</v>
       </c>
       <c r="M36" t="n">
-        <v>0.1946</v>
+        <v>0.1961</v>
       </c>
       <c r="N36" t="n">
-        <v>4.6252</v>
+        <v>4.6254</v>
       </c>
       <c r="O36" t="n">
-        <v>0.1146</v>
+        <v>0.1148</v>
       </c>
       <c r="P36" t="n">
-        <v>0.1146</v>
+        <v>0.1148</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.0547</v>
+        <v>0.0546</v>
       </c>
       <c r="R36" t="n">
-        <v>0.0328</v>
+        <v>0.0329</v>
       </c>
       <c r="S36" t="n">
-        <v>3753</v>
+        <v>3754</v>
       </c>
       <c r="T36" t="n">
-        <v>2.6055</v>
+        <v>2.6065</v>
       </c>
       <c r="U36" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="V36" t="n">
-        <v>2.4676</v>
+        <v>2.4661</v>
       </c>
       <c r="W36" t="n">
-        <v>1.6321</v>
+        <v>1.6301</v>
       </c>
       <c r="X36" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
@@ -3770,37 +3770,37 @@
         <v>74.46046</v>
       </c>
       <c r="C37" t="n">
-        <v>169.9091</v>
+        <v>169.90911</v>
       </c>
       <c r="D37" t="n">
         <v>39</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.4848</v>
+        <v>-1.4855</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.4845</v>
+        <v>-1.4852</v>
       </c>
       <c r="G37" t="n">
-        <v>24.032359</v>
+        <v>24.032612</v>
       </c>
       <c r="H37" t="n">
-        <v>24.031528</v>
+        <v>24.031694</v>
       </c>
       <c r="I37" t="n">
-        <v>29.838</v>
+        <v>29.8409</v>
       </c>
       <c r="J37" t="n">
-        <v>29.8365</v>
+        <v>29.8393</v>
       </c>
       <c r="K37" t="n">
-        <v>338.293</v>
+        <v>337.915</v>
       </c>
       <c r="L37" t="n">
-        <v>216.514</v>
+        <v>216.118</v>
       </c>
       <c r="M37" t="n">
-        <v>0.2386</v>
+        <v>0.2416</v>
       </c>
       <c r="N37" t="n">
         <v>4.6253</v>
@@ -3815,25 +3815,25 @@
         <v>0.0547</v>
       </c>
       <c r="R37" t="n">
-        <v>0.0346</v>
+        <v>0.0347</v>
       </c>
       <c r="S37" t="n">
-        <v>3806</v>
+        <v>3807</v>
       </c>
       <c r="T37" t="n">
-        <v>2.6421</v>
+        <v>2.6433</v>
       </c>
       <c r="U37" t="n">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="V37" t="n">
-        <v>2.406</v>
+        <v>2.4039</v>
       </c>
       <c r="W37" t="n">
-        <v>1.5536</v>
+        <v>1.5517</v>
       </c>
       <c r="X37" t="n">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="Y37" t="n">
         <v>0</v>
@@ -3856,7 +3856,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>39.582</v>
+        <v>39.583</v>
       </c>
       <c r="B38" t="n">
         <v>74.46046</v>
@@ -3871,61 +3871,61 @@
         <v>-1.4618</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.4609</v>
+        <v>-1.4611</v>
       </c>
       <c r="G38" t="n">
-        <v>24.1055</v>
+        <v>24.107073</v>
       </c>
       <c r="H38" t="n">
-        <v>24.105145</v>
+        <v>24.106602</v>
       </c>
       <c r="I38" t="n">
-        <v>29.9139</v>
+        <v>29.9167</v>
       </c>
       <c r="J38" t="n">
-        <v>29.9125</v>
+        <v>29.9153</v>
       </c>
       <c r="K38" t="n">
-        <v>324.617</v>
+        <v>324.12</v>
       </c>
       <c r="L38" t="n">
-        <v>208.907</v>
+        <v>215.216</v>
       </c>
       <c r="M38" t="n">
-        <v>0.5023</v>
+        <v>0.514</v>
       </c>
       <c r="N38" t="n">
-        <v>4.6258</v>
+        <v>4.6256</v>
       </c>
       <c r="O38" t="n">
-        <v>0.1179</v>
+        <v>0.1176</v>
       </c>
       <c r="P38" t="n">
-        <v>0.1179</v>
+        <v>0.1176</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.0543</v>
+        <v>0.0545</v>
       </c>
       <c r="R38" t="n">
-        <v>0.0451</v>
+        <v>0.0456</v>
       </c>
       <c r="S38" t="n">
-        <v>3858</v>
+        <v>3860</v>
       </c>
       <c r="T38" t="n">
-        <v>2.6788</v>
+        <v>2.6797</v>
       </c>
       <c r="U38" t="n">
-        <v>6.77</v>
+        <v>7.45</v>
       </c>
       <c r="V38" t="n">
-        <v>2.3308</v>
+        <v>2.328</v>
       </c>
       <c r="W38" t="n">
-        <v>1.5184</v>
+        <v>1.5487</v>
       </c>
       <c r="X38" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="Y38" t="n">
         <v>0</v>
@@ -3960,64 +3960,64 @@
         <v>41</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.4513</v>
+        <v>-1.4511</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.451</v>
+        <v>-1.4507</v>
       </c>
       <c r="G39" t="n">
-        <v>24.19156</v>
+        <v>24.194845</v>
       </c>
       <c r="H39" t="n">
-        <v>24.190887</v>
+        <v>24.194256</v>
       </c>
       <c r="I39" t="n">
-        <v>30.0199</v>
+        <v>30.0242</v>
       </c>
       <c r="J39" t="n">
-        <v>30.0186</v>
+        <v>30.023</v>
       </c>
       <c r="K39" t="n">
-        <v>309.999</v>
+        <v>309.726</v>
       </c>
       <c r="L39" t="n">
-        <v>295.075</v>
+        <v>295.993</v>
       </c>
       <c r="M39" t="n">
-        <v>1.0276</v>
+        <v>1.0385</v>
       </c>
       <c r="N39" t="n">
-        <v>4.6243</v>
+        <v>4.6236</v>
       </c>
       <c r="O39" t="n">
-        <v>0.1186</v>
+        <v>0.1184</v>
       </c>
       <c r="P39" t="n">
-        <v>0.1186</v>
+        <v>0.1184</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.0556</v>
+        <v>0.0562</v>
       </c>
       <c r="R39" t="n">
-        <v>0.0661</v>
+        <v>0.0666</v>
       </c>
       <c r="S39" t="n">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="T39" t="n">
-        <v>2.7209</v>
+        <v>2.7221</v>
       </c>
       <c r="U39" t="n">
-        <v>8.67</v>
+        <v>8.79</v>
       </c>
       <c r="V39" t="n">
-        <v>2.2498</v>
+        <v>2.2483</v>
       </c>
       <c r="W39" t="n">
-        <v>1.9322</v>
+        <v>1.9367</v>
       </c>
       <c r="X39" t="n">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="Y39" t="n">
         <v>0</v>
@@ -4040,76 +4040,76 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>41.56</v>
+        <v>41.562</v>
       </c>
       <c r="B40" t="n">
         <v>74.46046</v>
       </c>
       <c r="C40" t="n">
-        <v>169.90917</v>
+        <v>169.90918</v>
       </c>
       <c r="D40" t="n">
         <v>42</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.4278</v>
+        <v>-1.4259</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.4261</v>
+        <v>-1.4243</v>
       </c>
       <c r="G40" t="n">
-        <v>24.353305</v>
+        <v>24.36316</v>
       </c>
       <c r="H40" t="n">
-        <v>24.356221</v>
+        <v>24.365939</v>
       </c>
       <c r="I40" t="n">
-        <v>30.2155</v>
+        <v>30.2264</v>
       </c>
       <c r="J40" t="n">
-        <v>30.2178</v>
+        <v>30.2285</v>
       </c>
       <c r="K40" t="n">
-        <v>300.408</v>
+        <v>300.042</v>
       </c>
       <c r="L40" t="n">
-        <v>297.111</v>
+        <v>296.301</v>
       </c>
       <c r="M40" t="n">
-        <v>2.0888</v>
+        <v>2.0824</v>
       </c>
       <c r="N40" t="n">
-        <v>4.6127</v>
+        <v>4.6134</v>
       </c>
       <c r="O40" t="n">
-        <v>0.1206</v>
+        <v>0.1207</v>
       </c>
       <c r="P40" t="n">
-        <v>0.1206</v>
+        <v>0.1207</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.0656</v>
+        <v>0.065</v>
       </c>
       <c r="R40" t="n">
-        <v>0.1086</v>
+        <v>0.1083</v>
       </c>
       <c r="S40" t="n">
-        <v>3978</v>
+        <v>3980</v>
       </c>
       <c r="T40" t="n">
-        <v>2.7621</v>
+        <v>2.7632</v>
       </c>
       <c r="U40" t="n">
-        <v>10.88</v>
+        <v>10.73</v>
       </c>
       <c r="V40" t="n">
-        <v>2.1991</v>
+        <v>2.1972</v>
       </c>
       <c r="W40" t="n">
-        <v>1.9451</v>
+        <v>1.9414</v>
       </c>
       <c r="X40" t="n">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="Y40" t="n">
         <v>0</v>
@@ -4144,64 +4144,64 @@
         <v>43</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.4047</v>
+        <v>-1.4038</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.405</v>
+        <v>-1.4041</v>
       </c>
       <c r="G41" t="n">
-        <v>24.631378</v>
+        <v>24.645275</v>
       </c>
       <c r="H41" t="n">
-        <v>24.61932</v>
+        <v>24.63301</v>
       </c>
       <c r="I41" t="n">
-        <v>30.57</v>
+        <v>30.5871</v>
       </c>
       <c r="J41" t="n">
-        <v>30.5539</v>
+        <v>30.5708</v>
       </c>
       <c r="K41" t="n">
-        <v>277.26</v>
+        <v>275.67</v>
       </c>
       <c r="L41" t="n">
-        <v>277.106</v>
+        <v>275.726</v>
       </c>
       <c r="M41" t="n">
-        <v>1.2086</v>
+        <v>1.1836</v>
       </c>
       <c r="N41" t="n">
-        <v>4.5701</v>
+        <v>4.5669</v>
       </c>
       <c r="O41" t="n">
-        <v>0.1233</v>
+        <v>0.1234</v>
       </c>
       <c r="P41" t="n">
-        <v>0.1233</v>
+        <v>0.1234</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.1029</v>
+        <v>0.1056</v>
       </c>
       <c r="R41" t="n">
-        <v>0.0733</v>
+        <v>0.0723</v>
       </c>
       <c r="S41" t="n">
-        <v>4079</v>
+        <v>4085</v>
       </c>
       <c r="T41" t="n">
-        <v>2.8317</v>
+        <v>2.8358</v>
       </c>
       <c r="U41" t="n">
-        <v>3.31</v>
+        <v>3.91</v>
       </c>
       <c r="V41" t="n">
-        <v>2.0728</v>
+        <v>2.064</v>
       </c>
       <c r="W41" t="n">
-        <v>1.8532</v>
+        <v>1.8468</v>
       </c>
       <c r="X41" t="n">
-        <v>23</v>
+        <v>147</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
@@ -4224,76 +4224,76 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>43.539</v>
+        <v>43.538</v>
       </c>
       <c r="B42" t="n">
         <v>74.46046</v>
       </c>
       <c r="C42" t="n">
-        <v>169.90926</v>
+        <v>169.90927</v>
       </c>
       <c r="D42" t="n">
         <v>44</v>
       </c>
       <c r="E42" t="n">
-        <v>-1.3742</v>
+        <v>-1.3736</v>
       </c>
       <c r="F42" t="n">
-        <v>-1.3733</v>
+        <v>-1.3725</v>
       </c>
       <c r="G42" t="n">
-        <v>25.008419</v>
+        <v>25.018082</v>
       </c>
       <c r="H42" t="n">
-        <v>25.012228</v>
+        <v>25.022221</v>
       </c>
       <c r="I42" t="n">
-        <v>31.0517</v>
+        <v>31.0629</v>
       </c>
       <c r="J42" t="n">
-        <v>31.0559</v>
+        <v>31.0674</v>
       </c>
       <c r="K42" t="n">
-        <v>249.194</v>
+        <v>248.328</v>
       </c>
       <c r="L42" t="n">
-        <v>250.196</v>
+        <v>249.396</v>
       </c>
       <c r="M42" t="n">
-        <v>1.2229</v>
+        <v>1.2014</v>
       </c>
       <c r="N42" t="n">
-        <v>4.5283</v>
+        <v>4.5271</v>
       </c>
       <c r="O42" t="n">
-        <v>0.1269</v>
+        <v>0.1272</v>
       </c>
       <c r="P42" t="n">
-        <v>0.1269</v>
+        <v>0.1272</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.1396</v>
+        <v>0.1406</v>
       </c>
       <c r="R42" t="n">
-        <v>0.0739</v>
+        <v>0.0731</v>
       </c>
       <c r="S42" t="n">
-        <v>4189</v>
+        <v>4192</v>
       </c>
       <c r="T42" t="n">
-        <v>2.9083</v>
+        <v>2.9105</v>
       </c>
       <c r="U42" t="n">
-        <v>13.58</v>
+        <v>13.95</v>
       </c>
       <c r="V42" t="n">
-        <v>1.9195</v>
+        <v>1.9147</v>
       </c>
       <c r="W42" t="n">
-        <v>1.7295</v>
+        <v>1.7257</v>
       </c>
       <c r="X42" t="n">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="Y42" t="n">
         <v>0</v>
@@ -4328,64 +4328,64 @@
         <v>45</v>
       </c>
       <c r="E43" t="n">
-        <v>-1.3528</v>
+        <v>-1.3521</v>
       </c>
       <c r="F43" t="n">
-        <v>-1.3527</v>
+        <v>-1.3523</v>
       </c>
       <c r="G43" t="n">
-        <v>25.342905</v>
+        <v>25.352643</v>
       </c>
       <c r="H43" t="n">
-        <v>25.336031</v>
+        <v>25.342432</v>
       </c>
       <c r="I43" t="n">
-        <v>31.4848</v>
+        <v>31.4959</v>
       </c>
       <c r="J43" t="n">
-        <v>31.4754</v>
+        <v>31.4823</v>
       </c>
       <c r="K43" t="n">
-        <v>235.137</v>
+        <v>235.168</v>
       </c>
       <c r="L43" t="n">
-        <v>236.173</v>
+        <v>236.172</v>
       </c>
       <c r="M43" t="n">
-        <v>0.8199</v>
+        <v>0.7997</v>
       </c>
       <c r="N43" t="n">
-        <v>4.5288</v>
+        <v>4.5268</v>
       </c>
       <c r="O43" t="n">
-        <v>0.1289</v>
+        <v>0.1288</v>
       </c>
       <c r="P43" t="n">
-        <v>0.1289</v>
+        <v>0.1288</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.1392</v>
+        <v>0.1409</v>
       </c>
       <c r="R43" t="n">
-        <v>0.0578</v>
+        <v>0.057</v>
       </c>
       <c r="S43" t="n">
-        <v>4268</v>
+        <v>4269</v>
       </c>
       <c r="T43" t="n">
-        <v>2.9629</v>
+        <v>2.9638</v>
       </c>
       <c r="U43" t="n">
-        <v>6.71</v>
+        <v>6.25</v>
       </c>
       <c r="V43" t="n">
-        <v>1.8442</v>
+        <v>1.8446</v>
       </c>
       <c r="W43" t="n">
-        <v>1.6659</v>
+        <v>1.666</v>
       </c>
       <c r="X43" t="n">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="Y43" t="n">
         <v>0</v>
@@ -4408,10 +4408,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>45.518</v>
+        <v>45.519</v>
       </c>
       <c r="B44" t="n">
-        <v>74.46046</v>
+        <v>74.46047</v>
       </c>
       <c r="C44" t="n">
         <v>169.90934</v>
@@ -4420,64 +4420,64 @@
         <v>46</v>
       </c>
       <c r="E44" t="n">
-        <v>-1.3175</v>
+        <v>-1.3161</v>
       </c>
       <c r="F44" t="n">
-        <v>-1.3172</v>
+        <v>-1.3158</v>
       </c>
       <c r="G44" t="n">
-        <v>25.888391</v>
+        <v>25.910104</v>
       </c>
       <c r="H44" t="n">
-        <v>25.886791</v>
+        <v>25.905081</v>
       </c>
       <c r="I44" t="n">
-        <v>32.1917</v>
+        <v>32.218</v>
       </c>
       <c r="J44" t="n">
-        <v>32.1892</v>
+        <v>32.2109</v>
       </c>
       <c r="K44" t="n">
-        <v>214.036</v>
+        <v>212.599</v>
       </c>
       <c r="L44" t="n">
-        <v>216.058</v>
+        <v>214.716</v>
       </c>
       <c r="M44" t="n">
-        <v>0.5585</v>
+        <v>0.5152</v>
       </c>
       <c r="N44" t="n">
-        <v>4.5536</v>
+        <v>4.553</v>
       </c>
       <c r="O44" t="n">
-        <v>0.13</v>
+        <v>0.1301</v>
       </c>
       <c r="P44" t="n">
-        <v>0.13</v>
+        <v>0.1301</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.1173</v>
+        <v>0.1178</v>
       </c>
       <c r="R44" t="n">
-        <v>0.0473</v>
+        <v>0.0456</v>
       </c>
       <c r="S44" t="n">
-        <v>4359</v>
+        <v>4365</v>
       </c>
       <c r="T44" t="n">
-        <v>3.0262</v>
+        <v>3.0303</v>
       </c>
       <c r="U44" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="V44" t="n">
-        <v>1.7309</v>
+        <v>1.7229</v>
       </c>
       <c r="W44" t="n">
-        <v>1.5751</v>
+        <v>1.5687</v>
       </c>
       <c r="X44" t="n">
-        <v>26</v>
+        <v>116</v>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
@@ -4500,7 +4500,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>46.508</v>
+        <v>46.51</v>
       </c>
       <c r="B45" t="n">
         <v>74.46048</v>
@@ -4512,64 +4512,64 @@
         <v>47</v>
       </c>
       <c r="E45" t="n">
-        <v>-1.284</v>
+        <v>-1.2836</v>
       </c>
       <c r="F45" t="n">
-        <v>-1.284</v>
+        <v>-1.2835</v>
       </c>
       <c r="G45" t="n">
-        <v>26.414877</v>
+        <v>26.426821</v>
       </c>
       <c r="H45" t="n">
-        <v>26.410331</v>
+        <v>26.43125</v>
       </c>
       <c r="I45" t="n">
-        <v>32.8748</v>
+        <v>32.8892</v>
       </c>
       <c r="J45" t="n">
-        <v>32.8686</v>
+        <v>32.8951</v>
       </c>
       <c r="K45" t="n">
-        <v>183.004</v>
+        <v>182.43</v>
       </c>
       <c r="L45" t="n">
-        <v>186.187</v>
+        <v>185.708</v>
       </c>
       <c r="M45" t="n">
-        <v>0.3413</v>
+        <v>0.3517</v>
       </c>
       <c r="N45" t="n">
-        <v>4.5735</v>
+        <v>4.5742</v>
       </c>
       <c r="O45" t="n">
-        <v>0.1319</v>
+        <v>0.1321</v>
       </c>
       <c r="P45" t="n">
-        <v>0.1319</v>
+        <v>0.1321</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.0998</v>
+        <v>0.0992</v>
       </c>
       <c r="R45" t="n">
-        <v>0.0387</v>
+        <v>0.0391</v>
       </c>
       <c r="S45" t="n">
-        <v>4492</v>
+        <v>4493</v>
       </c>
       <c r="T45" t="n">
-        <v>3.119</v>
+        <v>3.1196</v>
       </c>
       <c r="U45" t="n">
-        <v>0.65</v>
+        <v>0.59</v>
       </c>
       <c r="V45" t="n">
-        <v>1.5583</v>
+        <v>1.5551</v>
       </c>
       <c r="W45" t="n">
-        <v>1.435</v>
+        <v>1.4328</v>
       </c>
       <c r="X45" t="n">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="Y45" t="n">
         <v>0</v>
